--- a/Result/profitability/4906.xlsx
+++ b/Result/profitability/4906.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.71</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1</v>
+        <v>0.05875</v>
       </c>
       <c r="N2" t="n">
-        <v>12.85</v>
+        <v>12.73875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0.27125</v>
+        <v>0.205</v>
       </c>
       <c r="N3" t="n">
-        <v>12.8425</v>
+        <v>13.03125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.63</v>
       </c>
       <c r="M4" t="n">
-        <v>0.42125</v>
+        <v>0.39</v>
       </c>
       <c r="N4" t="n">
-        <v>13.19625</v>
+        <v>13.2025</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.95</v>
       </c>
       <c r="M5" t="n">
-        <v>0.52125</v>
+        <v>0.62875</v>
       </c>
       <c r="N5" t="n">
-        <v>13.2425</v>
+        <v>13.08125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.88</v>
       </c>
       <c r="M6" t="n">
-        <v>0.75125</v>
+        <v>0.69375</v>
       </c>
       <c r="N6" t="n">
-        <v>13.0875</v>
+        <v>12.56375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.59</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7799999999999999</v>
+        <v>0.7424999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>12.5425</v>
+        <v>12.2925</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7987500000000001</v>
+        <v>0.8262499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>12.47875</v>
+        <v>12.705</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0.93875</v>
+        <v>0.9387500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>12.815</v>
@@ -1645,7 +1645,7 @@
         <v>0.54</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9175</v>
+        <v>0.9175000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>12.775</v>
@@ -1899,7 +1899,7 @@
         <v>0.27</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6062500000000001</v>
+        <v>0.60625</v>
       </c>
       <c r="N12" t="n">
         <v>12.16875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4906</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3613</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3174</v>
+      </c>
+      <c r="E75" t="n">
+        <v>439</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-116</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.21%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>62</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-54</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-46</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.001249999999999991</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.785</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6875</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1748792270531401</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8958333333333334</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.289999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.09591078066914493</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
